--- a/Proiect/Proiect/Output/Rapoarte/Rezultate_Lasso_Ridge.xlsx
+++ b/Proiect/Proiect/Output/Rapoarte/Rezultate_Lasso_Ridge.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>-7.355576497163903</v>
+        <v>2.03869118454188</v>
       </c>
       <c r="C2">
-        <v>-6.379765687800495</v>
+        <v>-2.73488376554052</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.981894792652293</v>
+        <v>0.3588614355122884</v>
       </c>
       <c r="C3">
-        <v>1.028997308426068</v>
+        <v>0.568060252140318</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.5699445579377833</v>
+        <v>0.3406712996541356</v>
       </c>
       <c r="C4">
-        <v>0.843211560887686</v>
+        <v>0.5013407600859361</v>
       </c>
     </row>
     <row r="5">
@@ -417,48 +417,35 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.1829802803029371</v>
+        <v>0.3110721982652647</v>
       </c>
       <c r="C5">
-        <v>0.07011461892238052</v>
+        <v>0.4169070542845448</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ln_Politie</t>
+          <t>ln_Densitate</t>
         </is>
       </c>
       <c r="B6">
-        <v>0.3078265229724558</v>
+        <v>-0.0830184817752349</v>
       </c>
       <c r="C6">
-        <v>0.1430366386682206</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ln_Densitate</t>
+          <t>Est_Vest</t>
         </is>
       </c>
       <c r="B7">
-        <v>-0.03862065899836679</v>
+        <v>-0.4074036334874997</v>
       </c>
       <c r="C7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Membru_UE</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>0.106995485073339</v>
-      </c>
-      <c r="C8">
         <v>0</v>
       </c>
     </row>
